--- a/lr1.xlsx
+++ b/lr1.xlsx
@@ -599,8 +599,8 @@
       <c r="I3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>16</v>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>16</v>
@@ -865,8 +865,8 @@
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>19</v>
+      <c r="C10" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -1260,45 +1260,6 @@
     <row r="31">
       <c r="A31" s="7"/>
     </row>
-    <row r="32">
-      <c r="A32" s="7"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/lr1.xlsx
+++ b/lr1.xlsx
@@ -64,22 +64,22 @@
     <t>1:n</t>
   </si>
   <si>
+    <t>n:1</t>
+  </si>
+  <si>
+    <t>E2 Отделение</t>
+  </si>
+  <si>
+    <t>E3 Тип отд.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1:n </t>
+  </si>
+  <si>
+    <t>E4 Док. займа</t>
+  </si>
+  <si>
     <t>1:1</t>
-  </si>
-  <si>
-    <t>E2 Отделение</t>
-  </si>
-  <si>
-    <t>n:1</t>
-  </si>
-  <si>
-    <t>E3 Тип отд.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1:n </t>
-  </si>
-  <si>
-    <t>E4 Док. займа</t>
   </si>
   <si>
     <t>E5 План выплат</t>
@@ -546,8 +546,8 @@
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>16</v>
@@ -582,7 +582,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>16</v>
@@ -614,13 +614,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -655,37 +655,37 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="I5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>14</v>
@@ -708,13 +708,13 @@
         <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>14</v>
@@ -740,7 +740,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>14</v>
@@ -767,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>14</v>
@@ -781,7 +781,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>14</v>
@@ -790,7 +790,7 @@
         <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>14</v>
@@ -808,7 +808,7 @@
         <v>14</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>14</v>
@@ -872,7 +872,7 @@
         <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>14</v>
@@ -884,13 +884,13 @@
         <v>14</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>14</v>
@@ -907,7 +907,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>14</v>
@@ -934,7 +934,7 @@
         <v>14</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>14</v>
@@ -986,7 +986,7 @@
         <v>30</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>14</v>
